--- a/assets/ideas.xlsx
+++ b/assets/ideas.xlsx
@@ -40,7 +40,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -48,12 +48,31 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="標準" xfId="0" builtinId="0"/>
@@ -397,7 +416,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G13"/>
+  <dimension ref="A1:H13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -434,6 +453,11 @@
       <c r="G1" t="inlineStr">
         <is>
           <t>output_filename</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>output_datetime</t>
         </is>
       </c>
     </row>
@@ -475,6 +499,7 @@
         </is>
       </c>
       <c r="G2" t="inlineStr"/>
+      <c r="H2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -514,6 +539,7 @@
         </is>
       </c>
       <c r="G3" t="inlineStr"/>
+      <c r="H3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -553,6 +579,7 @@
         </is>
       </c>
       <c r="G4" t="inlineStr"/>
+      <c r="H4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -588,10 +615,19 @@
       <c r="E5" t="inlineStr"/>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ready</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr"/>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>4.0_もうやってる_ 50代から密かに差がつく習慣</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>2026/01/31 13:53:31</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -631,6 +667,7 @@
         </is>
       </c>
       <c r="G6" t="inlineStr"/>
+      <c r="H6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -670,6 +707,7 @@
         </is>
       </c>
       <c r="G7" t="inlineStr"/>
+      <c r="H7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -709,6 +747,7 @@
         </is>
       </c>
       <c r="G8" t="inlineStr"/>
+      <c r="H8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -748,6 +787,7 @@
         </is>
       </c>
       <c r="G9" t="inlineStr"/>
+      <c r="H9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -787,6 +827,7 @@
         </is>
       </c>
       <c r="G10" t="inlineStr"/>
+      <c r="H10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -826,6 +867,7 @@
         </is>
       </c>
       <c r="G11" t="inlineStr"/>
+      <c r="H11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr"/>
@@ -863,6 +905,7 @@
         </is>
       </c>
       <c r="G12" t="inlineStr"/>
+      <c r="H12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr"/>
@@ -899,6 +942,7 @@
         </is>
       </c>
       <c r="G13" t="inlineStr"/>
+      <c r="H13" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/assets/ideas.xlsx
+++ b/assets/ideas.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\002__DEV\projects\ShortVideoMaker\assets\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BAD27DC7-7407-4A0B-A026-ED094DEC2E63}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B1FBBE1B-350F-49A1-B252-A15D70018C23}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="60" yWindow="-18120" windowWidth="29040" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="62" uniqueCount="51">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="45">
   <si>
     <t>id</t>
   </si>
@@ -140,12 +140,6 @@
     <t>#50代 #習慣 #人生</t>
   </si>
   <si>
-    <t>4.0_もうやってる_ 50代から密かに差がつく習慣</t>
-  </si>
-  <si>
-    <t>2026/01/31 13:53:31</t>
-  </si>
-  <si>
     <t>何個やっている？
 50代から体を守る基本習慣</t>
   </si>
@@ -167,12 +161,6 @@
     <t>#50代 #健康 #生活</t>
   </si>
   <si>
-    <t>5.0_何個やっている_ 50代から体を守る基本習慣</t>
-  </si>
-  <si>
-    <t>2026/01/31 14:16:22</t>
-  </si>
-  <si>
     <t>50代が知っておくべき
 令和の新常識</t>
   </si>
@@ -192,12 +180,6 @@
   </si>
   <si>
     <t>#50代 #常識 #令和</t>
-  </si>
-  <si>
-    <t>6.0_50代が知っておくべき 令和の新常識</t>
-  </si>
-  <si>
-    <t>2026/01/31 14:17:39</t>
   </si>
   <si>
     <t>50代から幸運を引き寄せる人
@@ -688,13 +670,13 @@
   <dimension ref="A1:H14"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
   <cols>
-    <col min="1" max="1" width="6.25" style="1" customWidth="1"/>
+    <col min="1" max="1" width="4.625" style="1" customWidth="1"/>
     <col min="2" max="2" width="30.125" style="1" customWidth="1"/>
-    <col min="3" max="3" width="27.125" style="1" customWidth="1"/>
-    <col min="4" max="4" width="27.625" style="1" customWidth="1"/>
+    <col min="3" max="3" width="33.875" style="1" customWidth="1"/>
+    <col min="4" max="4" width="23.25" style="1" customWidth="1"/>
     <col min="5" max="5" width="51.625" style="1" customWidth="1"/>
     <col min="6" max="6" width="15" style="1" customWidth="1"/>
-    <col min="7" max="7" width="39.125" style="1" customWidth="1"/>
+    <col min="7" max="7" width="40.625" style="1" customWidth="1"/>
     <col min="8" max="8" width="31.5" style="1" customWidth="1"/>
     <col min="9" max="10" width="9" style="1" customWidth="1"/>
     <col min="11" max="16384" width="9" style="1"/>
@@ -732,7 +714,7 @@
         <v>1</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="C2" s="3" t="s">
         <v>8</v>
@@ -807,12 +789,8 @@
       <c r="F5" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="G5" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="H5" s="2" t="s">
-        <v>21</v>
-      </c>
+      <c r="G5" s="2"/>
+      <c r="H5" s="2"/>
     </row>
     <row r="6" spans="1:8" ht="225" customHeight="1">
       <c r="A6" s="2">
@@ -820,24 +798,20 @@
         <v>5</v>
       </c>
       <c r="B6" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="D6" s="2" t="s">
         <v>22</v>
-      </c>
-      <c r="C6" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>24</v>
       </c>
       <c r="E6" s="2"/>
       <c r="F6" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="G6" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="H6" s="2" t="s">
-        <v>26</v>
-      </c>
+      <c r="G6" s="2"/>
+      <c r="H6" s="2"/>
     </row>
     <row r="7" spans="1:8" ht="225" customHeight="1">
       <c r="A7" s="2">
@@ -845,24 +819,20 @@
         <v>6</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="E7" s="2"/>
       <c r="F7" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="G7" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="H7" s="2" t="s">
-        <v>31</v>
-      </c>
+      <c r="G7" s="2"/>
+      <c r="H7" s="2"/>
     </row>
     <row r="8" spans="1:8" ht="225" customHeight="1">
       <c r="A8" s="2">
@@ -870,13 +840,13 @@
         <v>7</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="E8" s="2"/>
       <c r="F8" s="2" t="s">
@@ -891,13 +861,13 @@
         <v>8</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="E9" s="2"/>
       <c r="F9" s="2" t="s">
@@ -912,13 +882,13 @@
         <v>9</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="E10" s="2"/>
       <c r="F10" s="2" t="s">
@@ -933,13 +903,13 @@
         <v>10</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>41</v>
+        <v>35</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="E11" s="2"/>
       <c r="F11" s="2" t="s">
@@ -954,13 +924,13 @@
         <v>11</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>45</v>
+        <v>39</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="E12" s="2"/>
       <c r="F12" s="2" t="s">
@@ -975,13 +945,13 @@
         <v>12</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="E13" s="2"/>
       <c r="F13" s="2" t="s">

--- a/assets/ideas.xlsx
+++ b/assets/ideas.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\002__DEV\projects\ShortVideoMaker\assets\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B1FBBE1B-350F-49A1-B252-A15D70018C23}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7A041705-A99A-401F-8203-718116C4C786}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="60" yWindow="-18120" windowWidth="29040" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="45">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="34">
   <si>
     <t>id</t>
   </si>
@@ -42,19 +42,26 @@
     <t>bullets</t>
   </si>
   <si>
+    <t>status</t>
+  </si>
+  <si>
+    <t>output_filename</t>
+  </si>
+  <si>
+    <t>output_datetime</t>
+  </si>
+  <si>
     <t>tags</t>
   </si>
   <si>
     <t>description</t>
   </si>
   <si>
-    <t>status</t>
-  </si>
-  <si>
-    <t>output_filename</t>
-  </si>
-  <si>
-    <t>output_datetime</t>
+    <t>issue_status</t>
+  </si>
+  <si>
+    <t>老後貧乏を招く
+50代の思考</t>
   </si>
   <si>
     <t>① 貯金額を見ない
@@ -71,11 +78,186 @@
 ⑫ まだ先だと思う</t>
   </si>
   <si>
-    <t>#50代 #老後 #お金</t>
-  </si>
-  <si>
-    <t>50代で人が離れる人
-の共通点</t>
+    <t>50代で放置すると
+一気に老ける習慣</t>
+  </si>
+  <si>
+    <t>① 朝食を抜く日が多い
+② 水分補給が少なすぎ
+③ 階段を避け続ける
+④ 検診結果を見ない
+⑤ 腹八分を意識しない
+⑥ 夜のスマホが長い
+⑦ 口呼吸が癖になる
+⑧ 歩幅が年々狭い
+⑨ 体の痛みを無視
+⑩ 休日に動かない
+⑪ 体重増加を放置
+⑫ まだ若いと思う</t>
+  </si>
+  <si>
+    <t>もうやってる？
+50代から密かに差がつく習慣</t>
+  </si>
+  <si>
+    <t>① 毎月お金の使い道を見直す
+② 毎朝1分ストレッチする
+③ 年下に自分から挨拶
+④ 定期検診を先に予約
+⑤ 使わない物を手放す
+⑥ 1日5分、気持ちを書く時間を作る
+⑦ 週1で一人散歩
+⑧ 学んだ事を人に話す
+⑨ 無理な付き合い断る
+⑩ 歯と口を本気でケア
+⑪ 老後にやりたい事をノートに貯める
+⑫ 新しい事を年1つ試す</t>
+  </si>
+  <si>
+    <t>何個やっている？
+50代から体を守る基本習慣</t>
+  </si>
+  <si>
+    <t>① 朝起きて水を飲む
+② 毎日10分は歩く
+③ 夜食を習慣化しない
+④ 寝る前スマホをやめる
+⑤ 歯と口のケア徹底
+⑥ 痛みを放置しない
+⑦ 年1回は検診を受ける
+⑧ 体重を毎週見る
+⑨ 深呼吸を意識する
+⑩ 休日も生活リズムを崩さない
+⑪ 食べ過ぎを認める
+⑫ 体の声を聞く</t>
+  </si>
+  <si>
+    <t>50代が知っておくべき
+令和の新常識</t>
+  </si>
+  <si>
+    <t>① 電話より文章が基本
+② 若者は雑談を求めない
+③ 長時間労働は評価外
+④ 健康は自己責任時代
+⑤ 現金だけは不安要素
+⑥ 会社は守ってくれない
+⑦ 年功序列は期待しない
+⑧ 学ばない人は置かれる
+⑨ 退職後も働く前提
+⑩ 空気読むより線引き
+⑪ 迷惑は即距離を置く
+⑫ 我慢は美徳ではない</t>
+  </si>
+  <si>
+    <t>Ready</t>
+  </si>
+  <si>
+    <t>50代から幸運を引き寄せる人
+の習慣</t>
+  </si>
+  <si>
+    <t>① 朝に今日の予定を確認
+② 靴とカバンを整える
+③ 小さな約束を守る
+④ 体調の変化に気づく
+⑤ 感謝を言葉に出す
+⑥ 嫌な誘いは断る
+⑦ 月1で身の回り整理
+⑧ 人の話を最後まで聞く
+⑨ 新しい事を少し試す
+⑩ 無理を我慢しない
+⑪ 運が良い人を真似る
+⑫ 自分を雑に扱わない</t>
+  </si>
+  <si>
+    <t>いくつ当てはまる？
+50代で見直すべき不健康習慣</t>
+  </si>
+  <si>
+    <t>① 朝食を抜くのが普通
+② 水をあまり飲まない
+③ 歩くのが面倒になる
+④ 夜更かしが習慣化
+⑤ 検診を後回しにする
+⑥ 痛みを年のせいに
+⑦ 早食いが直らない
+⑧ 歯のケアを軽視
+⑨ 休日はずっと座る
+⑩ ストレスを我慢する
+⑪ 体重を測らない
+⑫ まだ大丈夫と思う</t>
+  </si>
+  <si>
+    <t>50代から人間関係の
+運が良くなる習慣</t>
+  </si>
+  <si>
+    <t>① 自分から挨拶を出す
+② 相手の名前を呼ぶ
+③ 話を途中で遮らない
+④ 昔話を引きずらない
+⑤ 正論を急がない
+⑥ 愚痴は外で言わない
+⑦ 年下に教えを乞う
+⑧ 距離が合わない人は無理しない
+⑨ 小さな感謝を口に出す
+⑩ 返事を早めに返す
+⑪ 評価より理解を選ぶ
+⑫ 去る人を追わない</t>
+  </si>
+  <si>
+    <t>50代から取り組むべき
+リスキリング</t>
+  </si>
+  <si>
+    <t>① オンライン手続きをする
+② 分からないまま放置しない
+③ チャット文化に慣れる
+④ オンライン会議に慣れる
+⑤ AIを触ってみる
+⑥ 情報の真偽を見抜く
+⑦ お金の知識を更新
+⑧ 健康管理を数値で見る
+⑨ 教える側のスキル習得
+⑩ 副業の選択肢を知る
+⑪ 若者文化を理解する
+⑫ 学びをやめない癖</t>
+  </si>
+  <si>
+    <t>あなたは大丈夫？
+50代から気をつけたい口癖</t>
+  </si>
+  <si>
+    <t>①「もう歳だから」
+②「昔は良かった」
+③「でも」「だって」
+④「若いからだよ」
+⑤「どうせ変わらない」
+⑥「忙しいから無理」
+⑦「聞いてない」
+⑧「前にも言った」
+⑨「俺の時代は」
+⑩「面倒くさい」
+⑪「今さらやっても」
+⑫「そのうちやる」</t>
+  </si>
+  <si>
+    <t>50代で信頼される返事の仕方</t>
+  </si>
+  <si>
+    <t>① まず結論を言う
+② 返事は早めに
+③ 出来る事を伝える
+④ 無理は正直に言う
+⑤ 期限をはっきり
+⑥ 一度受け止める
+⑦ 曖昧にしない
+⑧ 感謝を添える
+⑨ 確認してから返す
+⑩ 言い切らず含み持たす
+⑪ 途中経過を伝える
+⑫ 約束は必ず守る</t>
   </si>
   <si>
     <t>① 昔話ばかりする
@@ -90,225 +272,11 @@
 ⑩ 空気を読まない
 ⑪ 感謝を言わない
 ⑫ 自分は例外と思う</t>
-  </si>
-  <si>
-    <t>#50代 #人間関係 #仕事</t>
-  </si>
-  <si>
-    <t>Ready</t>
-  </si>
-  <si>
-    <t>50代で放置すると
-一気に老ける習慣</t>
-  </si>
-  <si>
-    <t>① 朝食を抜く日が多い
-② 水分補給が少なすぎ
-③ 階段を避け続ける
-④ 検診結果を見ない
-⑤ 腹八分を意識しない
-⑥ 夜のスマホが長い
-⑦ 口呼吸が癖になる
-⑧ 歩幅が年々狭い
-⑨ 体の痛みを無視
-⑩ 休日に動かない
-⑪ 体重増加を放置
-⑫ まだ若いと思う</t>
-  </si>
-  <si>
-    <t>#50代 #健康 #老化</t>
-  </si>
-  <si>
-    <t>もうやってる？
-50代から密かに差がつく習慣</t>
-  </si>
-  <si>
-    <t>① 毎月お金の使い道を見直す
-② 毎朝1分ストレッチする
-③ 年下に自分から挨拶
-④ 定期検診を先に予約
-⑤ 使わない物を手放す
-⑥ 1日5分、気持ちを書く時間を作る
-⑦ 週1で一人散歩
-⑧ 学んだ事を人に話す
-⑨ 無理な付き合い断る
-⑩ 歯と口を本気でケア
-⑪ 老後にやりたい事をノートに貯める
-⑫ 新しい事を年1つ試す</t>
-  </si>
-  <si>
-    <t>#50代 #習慣 #人生</t>
-  </si>
-  <si>
-    <t>何個やっている？
-50代から体を守る基本習慣</t>
-  </si>
-  <si>
-    <t>① 朝起きて水を飲む
-② 毎日10分は歩く
-③ 夜食を習慣化しない
-④ 寝る前スマホをやめる
-⑤ 歯と口のケア徹底
-⑥ 痛みを放置しない
-⑦ 年1回は検診を受ける
-⑧ 体重を毎週見る
-⑨ 深呼吸を意識する
-⑩ 休日も生活リズムを崩さない
-⑪ 食べ過ぎを認める
-⑫ 体の声を聞く</t>
-  </si>
-  <si>
-    <t>#50代 #健康 #生活</t>
-  </si>
-  <si>
-    <t>50代が知っておくべき
-令和の新常識</t>
-  </si>
-  <si>
-    <t>① 電話より文章が基本
-② 若者は雑談を求めない
-③ 長時間労働は評価外
-④ 健康は自己責任時代
-⑤ 現金だけは不安要素
-⑥ 会社は守ってくれない
-⑦ 年功序列は期待しない
-⑧ 学ばない人は置かれる
-⑨ 退職後も働く前提
-⑩ 空気読むより線引き
-⑪ 迷惑は即距離を置く
-⑫ 我慢は美徳ではない</t>
-  </si>
-  <si>
-    <t>#50代 #常識 #令和</t>
-  </si>
-  <si>
-    <t>50代から幸運を引き寄せる人
-の習慣</t>
-  </si>
-  <si>
-    <t>① 朝に今日の予定を確認
-② 靴とカバンを整える
-③ 小さな約束を守る
-④ 体調の変化に気づく
-⑤ 感謝を言葉に出す
-⑥ 嫌な誘いは断る
-⑦ 月1で身の回り整理
-⑧ 人の話を最後まで聞く
-⑨ 新しい事を少し試す
-⑩ 無理を我慢しない
-⑪ 運が良い人を真似る
-⑫ 自分を雑に扱わない</t>
-  </si>
-  <si>
-    <t>#50代 #幸せ #考え方</t>
-  </si>
-  <si>
-    <t>いくつ当てはまる？
-50代で見直すべき不健康習慣</t>
-  </si>
-  <si>
-    <t>① 朝食を抜くのが普通
-② 水をあまり飲まない
-③ 歩くのが面倒になる
-④ 夜更かしが習慣化
-⑤ 検診を後回しにする
-⑥ 痛みを年のせいに
-⑦ 早食いが直らない
-⑧ 歯のケアを軽視
-⑨ 休日はずっと座る
-⑩ ストレスを我慢する
-⑪ 体重を測らない
-⑫ まだ大丈夫と思う</t>
-  </si>
-  <si>
-    <t>#50代 #健康 #習慣</t>
-  </si>
-  <si>
-    <t>50代から人間関係の
-運が良くなる習慣</t>
-  </si>
-  <si>
-    <t>① 自分から挨拶を出す
-② 相手の名前を呼ぶ
-③ 話を途中で遮らない
-④ 昔話を引きずらない
-⑤ 正論を急がない
-⑥ 愚痴は外で言わない
-⑦ 年下に教えを乞う
-⑧ 距離が合わない人は無理しない
-⑨ 小さな感謝を口に出す
-⑩ 返事を早めに返す
-⑪ 評価より理解を選ぶ
-⑫ 去る人を追わない</t>
-  </si>
-  <si>
-    <t>#50代 #人間関係 #習慣</t>
-  </si>
-  <si>
-    <t>50代から取り組むべき
-リスキリング</t>
-  </si>
-  <si>
-    <t>① オンライン手続きをする
-② 分からないまま放置しない
-③ チャット文化に慣れる
-④ オンライン会議に慣れる
-⑤ AIを触ってみる
-⑥ 情報の真偽を見抜く
-⑦ お金の知識を更新
-⑧ 健康管理を数値で見る
-⑨ 教える側のスキル習得
-⑩ 副業の選択肢を知る
-⑪ 若者文化を理解する
-⑫ 学びをやめない癖</t>
-  </si>
-  <si>
-    <t>#50代 #学び #仕事</t>
-  </si>
-  <si>
-    <t>あなたは大丈夫？
-50代から気をつけたい口癖</t>
-  </si>
-  <si>
-    <t>①「もう歳だから」
-②「昔は良かった」
-③「でも」「だって」
-④「若いからだよ」
-⑤「どうせ変わらない」
-⑥「忙しいから無理」
-⑦「聞いてない」
-⑧「前にも言った」
-⑨「俺の時代は」
-⑩「面倒くさい」
-⑪「今さらやっても」
-⑫「そのうちやる」</t>
-  </si>
-  <si>
-    <t>#50代 #口癖 #人間関係</t>
-  </si>
-  <si>
-    <t>50代で信頼される返事の仕方</t>
-  </si>
-  <si>
-    <t>① まず結論を言う
-② 返事は早めに
-③ 出来る事を伝える
-④ 無理は正直に言う
-⑤ 期限をはっきり
-⑥ 一度受け止める
-⑦ 曖昧にしない
-⑧ 感謝を添える
-⑨ 確認してから返す
-⑩ 言い切らず含み持たす
-⑪ 途中経過を伝える
-⑫ 約束は必ず守る</t>
-  </si>
-  <si>
-    <t>#50代 #仕事 #信頼</t>
-  </si>
-  <si>
-    <t>老後貧乏を招く
-50代の思考</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>50代で人が離れる人
+の共通点</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -667,22 +635,23 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H14"/>
+  <dimension ref="A1:I13"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
   <cols>
     <col min="1" max="1" width="4.625" style="1" customWidth="1"/>
-    <col min="2" max="2" width="30.125" style="1" customWidth="1"/>
+    <col min="2" max="2" width="26.125" style="1" customWidth="1"/>
     <col min="3" max="3" width="33.875" style="1" customWidth="1"/>
-    <col min="4" max="4" width="23.25" style="1" customWidth="1"/>
-    <col min="5" max="5" width="51.625" style="1" customWidth="1"/>
-    <col min="6" max="6" width="15" style="1" customWidth="1"/>
-    <col min="7" max="7" width="40.625" style="1" customWidth="1"/>
-    <col min="8" max="8" width="31.5" style="1" customWidth="1"/>
-    <col min="9" max="10" width="9" style="1" customWidth="1"/>
-    <col min="11" max="16384" width="9" style="1"/>
+    <col min="4" max="4" width="15" style="1" customWidth="1"/>
+    <col min="5" max="5" width="40.625" style="1" customWidth="1"/>
+    <col min="6" max="6" width="31.5" style="1" customWidth="1"/>
+    <col min="7" max="7" width="23.25" style="1" customWidth="1"/>
+    <col min="8" max="8" width="33.125" style="1" customWidth="1"/>
+    <col min="9" max="9" width="21.375" style="1" customWidth="1"/>
+    <col min="10" max="13" width="9" style="1" customWidth="1"/>
+    <col min="14" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8">
+    <row r="1" spans="1:9">
       <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
@@ -707,268 +676,249 @@
       <c r="H1" s="4" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="2" spans="1:8" ht="225" customHeight="1">
+      <c r="I1" s="4" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" ht="257.25" customHeight="1">
       <c r="A2" s="2">
-        <f>ROW()-1</f>
+        <f t="shared" ref="A2:A13" si="0">ROW()-1</f>
         <v>1</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>44</v>
+        <v>9</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="E2" s="2"/>
-      <c r="F2" s="2" t="s">
-        <v>13</v>
-      </c>
+      <c r="F2" s="2"/>
       <c r="G2" s="2"/>
       <c r="H2" s="2"/>
-    </row>
-    <row r="3" spans="1:8" ht="225" customHeight="1">
+      <c r="I2" s="2"/>
+    </row>
+    <row r="3" spans="1:9" ht="276.75" customHeight="1">
       <c r="A3" s="2">
-        <f t="shared" ref="A3:A13" si="0">ROW()-1</f>
+        <f t="shared" si="0"/>
         <v>2</v>
       </c>
-      <c r="B3" s="2" t="s">
-        <v>10</v>
+      <c r="B3" s="3" t="s">
+        <v>33</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>11</v>
+        <v>32</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="E3" s="2"/>
-      <c r="F3" s="2" t="s">
-        <v>13</v>
-      </c>
+      <c r="F3" s="2"/>
       <c r="G3" s="2"/>
       <c r="H3" s="2"/>
-    </row>
-    <row r="4" spans="1:8" ht="225" customHeight="1">
+      <c r="I3" s="2"/>
+    </row>
+    <row r="4" spans="1:9" ht="225" customHeight="1">
       <c r="A4" s="2">
         <f t="shared" si="0"/>
         <v>3</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="E4" s="2"/>
-      <c r="F4" s="2" t="s">
-        <v>13</v>
-      </c>
+      <c r="F4" s="2"/>
       <c r="G4" s="2"/>
       <c r="H4" s="2"/>
-    </row>
-    <row r="5" spans="1:8" ht="225" customHeight="1">
+      <c r="I4" s="2"/>
+    </row>
+    <row r="5" spans="1:9" ht="225" customHeight="1">
       <c r="A5" s="2">
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="D5" s="2" t="s">
         <v>19</v>
       </c>
       <c r="E5" s="2"/>
-      <c r="F5" s="2" t="s">
-        <v>13</v>
-      </c>
+      <c r="F5" s="2"/>
       <c r="G5" s="2"/>
       <c r="H5" s="2"/>
-    </row>
-    <row r="6" spans="1:8" ht="225" customHeight="1">
+      <c r="I5" s="2"/>
+    </row>
+    <row r="6" spans="1:9" ht="225" customHeight="1">
       <c r="A6" s="2">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="E6" s="2"/>
-      <c r="F6" s="2" t="s">
-        <v>13</v>
-      </c>
+      <c r="F6" s="2"/>
       <c r="G6" s="2"/>
       <c r="H6" s="2"/>
-    </row>
-    <row r="7" spans="1:8" ht="225" customHeight="1">
+      <c r="I6" s="2"/>
+    </row>
+    <row r="7" spans="1:9" ht="225" customHeight="1">
       <c r="A7" s="2">
         <f t="shared" si="0"/>
         <v>6</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="E7" s="2"/>
-      <c r="F7" s="2" t="s">
-        <v>13</v>
-      </c>
+      <c r="F7" s="2"/>
       <c r="G7" s="2"/>
       <c r="H7" s="2"/>
-    </row>
-    <row r="8" spans="1:8" ht="225" customHeight="1">
+      <c r="I7" s="2"/>
+    </row>
+    <row r="8" spans="1:9" ht="225" customHeight="1">
       <c r="A8" s="2">
         <f t="shared" si="0"/>
         <v>7</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>28</v>
+        <v>19</v>
       </c>
       <c r="E8" s="2"/>
-      <c r="F8" s="2" t="s">
-        <v>13</v>
-      </c>
+      <c r="F8" s="2"/>
       <c r="G8" s="2"/>
       <c r="H8" s="2"/>
-    </row>
-    <row r="9" spans="1:8" ht="225" customHeight="1">
+      <c r="I8" s="2"/>
+    </row>
+    <row r="9" spans="1:9" ht="225" customHeight="1">
       <c r="A9" s="2">
         <f t="shared" si="0"/>
         <v>8</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>31</v>
+        <v>19</v>
       </c>
       <c r="E9" s="2"/>
-      <c r="F9" s="2" t="s">
-        <v>13</v>
-      </c>
+      <c r="F9" s="2"/>
       <c r="G9" s="2"/>
       <c r="H9" s="2"/>
-    </row>
-    <row r="10" spans="1:8" ht="225" customHeight="1">
+      <c r="I9" s="2"/>
+    </row>
+    <row r="10" spans="1:9" ht="225" customHeight="1">
       <c r="A10" s="2">
         <f t="shared" si="0"/>
         <v>9</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>33</v>
+        <v>25</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>34</v>
+        <v>19</v>
       </c>
       <c r="E10" s="2"/>
-      <c r="F10" s="2" t="s">
-        <v>13</v>
-      </c>
+      <c r="F10" s="2"/>
       <c r="G10" s="2"/>
       <c r="H10" s="2"/>
-    </row>
-    <row r="11" spans="1:8" ht="225" customHeight="1">
+      <c r="I10" s="2"/>
+    </row>
+    <row r="11" spans="1:9" ht="225" customHeight="1">
       <c r="A11" s="2">
         <f t="shared" si="0"/>
         <v>10</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>35</v>
+        <v>26</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>36</v>
+        <v>27</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>37</v>
+        <v>19</v>
       </c>
       <c r="E11" s="2"/>
-      <c r="F11" s="2" t="s">
-        <v>13</v>
-      </c>
+      <c r="F11" s="2"/>
       <c r="G11" s="2"/>
       <c r="H11" s="2"/>
-    </row>
-    <row r="12" spans="1:8" ht="225" customHeight="1">
+      <c r="I11" s="2"/>
+    </row>
+    <row r="12" spans="1:9" ht="225" customHeight="1">
       <c r="A12" s="2">
         <f t="shared" si="0"/>
         <v>11</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>38</v>
+        <v>28</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>39</v>
+        <v>29</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>40</v>
+        <v>19</v>
       </c>
       <c r="E12" s="2"/>
-      <c r="F12" s="2" t="s">
-        <v>13</v>
-      </c>
+      <c r="F12" s="2"/>
       <c r="G12" s="2"/>
       <c r="H12" s="2"/>
-    </row>
-    <row r="13" spans="1:8" ht="225" customHeight="1">
+      <c r="I12" s="2"/>
+    </row>
+    <row r="13" spans="1:9" ht="291.75" customHeight="1">
       <c r="A13" s="2">
         <f t="shared" si="0"/>
         <v>12</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>41</v>
+        <v>30</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>42</v>
+        <v>31</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>43</v>
+        <v>19</v>
       </c>
       <c r="E13" s="2"/>
-      <c r="F13" s="2" t="s">
-        <v>13</v>
-      </c>
+      <c r="F13" s="2"/>
       <c r="G13" s="2"/>
       <c r="H13" s="2"/>
-    </row>
-    <row r="14" spans="1:8">
-      <c r="A14" s="2"/>
-      <c r="B14" s="2"/>
-      <c r="C14" s="2"/>
-      <c r="D14" s="2"/>
-      <c r="E14" s="2"/>
-      <c r="F14" s="2"/>
-      <c r="G14" s="2"/>
-      <c r="H14" s="2"/>
+      <c r="I13" s="2"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1"/>
